--- a/artfynd/A 28376-2026 artfynd.xlsx
+++ b/artfynd/A 28376-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134919674</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129658167</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129658168</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038639</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1168,6 +1193,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129658161</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129658162</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1364,6 +1399,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129658163</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,6 +1502,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129658164</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129658165</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1658,6 +1708,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129658166</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1771,6 +1826,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038619</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1879,6 +1939,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038620</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038623</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2095,6 +2165,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038624</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2208,6 +2283,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038625</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2315,6 +2395,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038627</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2422,6 +2507,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038628</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2529,6 +2619,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038630</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2636,6 +2731,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038634</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2743,6 +2843,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038635</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2850,6 +2955,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038636</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2957,6 +3067,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038637</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3064,6 +3179,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038638</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3161,6 +3281,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134919546</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3258,6 +3383,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129658153</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3365,6 +3495,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038594</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3472,6 +3607,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038588</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3569,6 +3709,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134919695</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3676,6 +3821,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134919319</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3773,6 +3923,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134919718</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3875,6 +4030,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134919814</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3972,6 +4132,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129658155</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4085,6 +4250,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038589</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4187,6 +4357,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129658156</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4300,6 +4475,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038596</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4407,6 +4587,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038606</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4514,6 +4699,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038611</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4621,6 +4811,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038612</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4728,6 +4923,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038613</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4835,6 +5035,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038614</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4942,6 +5147,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038615</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5049,6 +5259,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038616</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5156,6 +5371,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132038617</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5262,6 +5482,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134919482</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5373,6 +5598,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134919526</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5479,6 +5709,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134919593</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5590,6 +5825,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134919613</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5696,6 +5936,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134919809</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5794,8 +6039,64 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129658154</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28376-2026 artfynd.xlsx
+++ b/artfynd/A 28376-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134919674</v>
       </c>
       <c r="B2" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>134919546</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>134919695</v>
       </c>
       <c r="B29" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>134919319</v>
       </c>
       <c r="B30" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>134919718</v>
       </c>
       <c r="B31" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>134919814</v>
       </c>
       <c r="B32" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>134919482</v>
       </c>
       <c r="B45" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>134919526</v>
       </c>
       <c r="B46" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>134919593</v>
       </c>
       <c r="B47" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>134919613</v>
       </c>
       <c r="B48" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>134919809</v>
       </c>
       <c r="B49" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 28376-2026 artfynd.xlsx
+++ b/artfynd/A 28376-2026 artfynd.xlsx
@@ -2111,7 +2111,7 @@
         <v>135694241</v>
       </c>
       <c r="B16" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>135695820</v>
       </c>
       <c r="B84" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>135693099</v>
       </c>
       <c r="B100" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>135693143</v>
       </c>
       <c r="B101" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>135693261</v>
       </c>
       <c r="B102" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>135693320</v>
       </c>
       <c r="B103" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>135693361</v>
       </c>
       <c r="B104" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>135693409</v>
       </c>
       <c r="B105" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>135693449</v>
       </c>
       <c r="B106" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>135694006</v>
       </c>
       <c r="B107" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>135694368</v>
       </c>
       <c r="B108" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>135695337</v>
       </c>
       <c r="B109" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>135695467</v>
       </c>
       <c r="B110" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>135695589</v>
       </c>
       <c r="B111" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>135695640</v>
       </c>
       <c r="B112" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>135695650</v>
       </c>
       <c r="B113" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>135695661</v>
       </c>
       <c r="B114" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>135695778</v>
       </c>
       <c r="B115" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>135695863</v>
       </c>
       <c r="B116" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>135695888</v>
       </c>
       <c r="B117" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>135695827</v>
       </c>
       <c r="B118" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 28376-2026 artfynd.xlsx
+++ b/artfynd/A 28376-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135693259</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135693412</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135693522</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135693681</v>
       </c>
       <c r="B5" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135693950</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135693987</v>
       </c>
       <c r="B7" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135694070</v>
       </c>
       <c r="B8" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135694346</v>
       </c>
       <c r="B9" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135694505</v>
       </c>
       <c r="B10" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135694965</v>
       </c>
       <c r="B11" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135695151</v>
       </c>
       <c r="B12" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135695441</v>
       </c>
       <c r="B13" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135693971</v>
       </c>
       <c r="B15" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135694241</v>
       </c>
       <c r="B16" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>135693150</v>
       </c>
       <c r="B40" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>135693173</v>
       </c>
       <c r="B41" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>135693178</v>
       </c>
       <c r="B42" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>135693517</v>
       </c>
       <c r="B43" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>135693630</v>
       </c>
       <c r="B44" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>135693671</v>
       </c>
       <c r="B45" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>135693676</v>
       </c>
       <c r="B46" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>135694781</v>
       </c>
       <c r="B47" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>135695032</v>
       </c>
       <c r="B48" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135695091</v>
       </c>
       <c r="B49" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>135695305</v>
       </c>
       <c r="B50" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>135695360</v>
       </c>
       <c r="B51" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>135695385</v>
       </c>
       <c r="B52" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>135695569</v>
       </c>
       <c r="B53" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>135695602</v>
       </c>
       <c r="B54" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>135695710</v>
       </c>
       <c r="B55" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>135695786</v>
       </c>
       <c r="B56" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>135695844</v>
       </c>
       <c r="B57" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>135694109</v>
       </c>
       <c r="B59" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>135693769</v>
       </c>
       <c r="B61" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>135695207</v>
       </c>
       <c r="B62" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>135695447</v>
       </c>
       <c r="B63" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>135693600</v>
       </c>
       <c r="B64" t="n">
-        <v>79527</v>
+        <v>79529</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>135694482</v>
       </c>
       <c r="B65" t="n">
-        <v>79527</v>
+        <v>79529</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>135694128</v>
       </c>
       <c r="B66" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>135694698</v>
       </c>
       <c r="B67" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>135695115</v>
       </c>
       <c r="B68" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>135695211</v>
       </c>
       <c r="B70" t="n">
-        <v>80560</v>
+        <v>80562</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>135694103</v>
       </c>
       <c r="B72" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>135694882</v>
       </c>
       <c r="B73" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>135695039</v>
       </c>
       <c r="B74" t="n">
-        <v>57629</v>
+        <v>57631</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>135694812</v>
       </c>
       <c r="B75" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>135695614</v>
       </c>
       <c r="B77" t="n">
-        <v>58415</v>
+        <v>58417</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>135693380</v>
       </c>
       <c r="B80" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>135695688</v>
       </c>
       <c r="B81" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>135695820</v>
       </c>
       <c r="B84" t="n">
-        <v>99180</v>
+        <v>99197</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>135693099</v>
       </c>
       <c r="B100" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>135693143</v>
       </c>
       <c r="B101" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>135693261</v>
       </c>
       <c r="B102" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>135693320</v>
       </c>
       <c r="B103" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>135693361</v>
       </c>
       <c r="B104" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>135693409</v>
       </c>
       <c r="B105" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>135693449</v>
       </c>
       <c r="B106" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>135694006</v>
       </c>
       <c r="B107" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>135694368</v>
       </c>
       <c r="B108" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>135695337</v>
       </c>
       <c r="B109" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>135695467</v>
       </c>
       <c r="B110" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>135695589</v>
       </c>
       <c r="B111" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>135695640</v>
       </c>
       <c r="B112" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>135695650</v>
       </c>
       <c r="B113" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>135695661</v>
       </c>
       <c r="B114" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>135695778</v>
       </c>
       <c r="B115" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>135695863</v>
       </c>
       <c r="B116" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>135695888</v>
       </c>
       <c r="B117" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>135695827</v>
       </c>
       <c r="B118" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>135693489</v>
       </c>
       <c r="B120" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>135693779</v>
       </c>
       <c r="B121" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>135695241</v>
       </c>
       <c r="B122" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>135695458</v>
       </c>
       <c r="B123" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>135695697</v>
       </c>
       <c r="B124" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>135694935</v>
       </c>
       <c r="B125" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>135695349</v>
       </c>
       <c r="B126" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 28376-2026 artfynd.xlsx
+++ b/artfynd/A 28376-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135693259</v>
       </c>
       <c r="B2" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135693412</v>
       </c>
       <c r="B3" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135693522</v>
       </c>
       <c r="B4" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135693681</v>
       </c>
       <c r="B5" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135693950</v>
       </c>
       <c r="B6" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135693987</v>
       </c>
       <c r="B7" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135694070</v>
       </c>
       <c r="B8" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135694346</v>
       </c>
       <c r="B9" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135694505</v>
       </c>
       <c r="B10" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135694965</v>
       </c>
       <c r="B11" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135695151</v>
       </c>
       <c r="B12" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135695441</v>
       </c>
       <c r="B13" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135693971</v>
       </c>
       <c r="B15" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135694241</v>
       </c>
       <c r="B16" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>135693150</v>
       </c>
       <c r="B40" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>135693173</v>
       </c>
       <c r="B41" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>135693178</v>
       </c>
       <c r="B42" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>135693517</v>
       </c>
       <c r="B43" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>135693630</v>
       </c>
       <c r="B44" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>135693671</v>
       </c>
       <c r="B45" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>135693676</v>
       </c>
       <c r="B46" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>135694781</v>
       </c>
       <c r="B47" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>135695032</v>
       </c>
       <c r="B48" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135695091</v>
       </c>
       <c r="B49" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>135695305</v>
       </c>
       <c r="B50" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>135695360</v>
       </c>
       <c r="B51" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>135695385</v>
       </c>
       <c r="B52" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>135695569</v>
       </c>
       <c r="B53" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>135695602</v>
       </c>
       <c r="B54" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>135695710</v>
       </c>
       <c r="B55" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>135695786</v>
       </c>
       <c r="B56" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>135695844</v>
       </c>
       <c r="B57" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>135694109</v>
       </c>
       <c r="B59" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>135693769</v>
       </c>
       <c r="B61" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>135695207</v>
       </c>
       <c r="B62" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>135695447</v>
       </c>
       <c r="B63" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>135693600</v>
       </c>
       <c r="B64" t="n">
-        <v>79529</v>
+        <v>79530</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>135694482</v>
       </c>
       <c r="B65" t="n">
-        <v>79529</v>
+        <v>79530</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>135694128</v>
       </c>
       <c r="B66" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>135694698</v>
       </c>
       <c r="B67" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>135695115</v>
       </c>
       <c r="B68" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>135695211</v>
       </c>
       <c r="B70" t="n">
-        <v>80562</v>
+        <v>80563</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>135694103</v>
       </c>
       <c r="B72" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>135694882</v>
       </c>
       <c r="B73" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>135695820</v>
       </c>
       <c r="B84" t="n">
-        <v>99197</v>
+        <v>99198</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>135693099</v>
       </c>
       <c r="B100" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>135693143</v>
       </c>
       <c r="B101" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>135693261</v>
       </c>
       <c r="B102" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>135693320</v>
       </c>
       <c r="B103" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>135693361</v>
       </c>
       <c r="B104" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>135693409</v>
       </c>
       <c r="B105" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>135693449</v>
       </c>
       <c r="B106" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>135694006</v>
       </c>
       <c r="B107" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>135694368</v>
       </c>
       <c r="B108" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>135695337</v>
       </c>
       <c r="B109" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>135695467</v>
       </c>
       <c r="B110" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>135695589</v>
       </c>
       <c r="B111" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>135695640</v>
       </c>
       <c r="B112" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>135695650</v>
       </c>
       <c r="B113" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>135695661</v>
       </c>
       <c r="B114" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>135695778</v>
       </c>
       <c r="B115" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>135695863</v>
       </c>
       <c r="B116" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>135695888</v>
       </c>
       <c r="B117" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>135695827</v>
       </c>
       <c r="B118" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>135693489</v>
       </c>
       <c r="B120" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>135693779</v>
       </c>
       <c r="B121" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>135695241</v>
       </c>
       <c r="B122" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>135695458</v>
       </c>
       <c r="B123" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>135695697</v>
       </c>
       <c r="B124" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>135694935</v>
       </c>
       <c r="B125" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>135695349</v>
       </c>
       <c r="B126" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 28376-2026 artfynd.xlsx
+++ b/artfynd/A 28376-2026 artfynd.xlsx
@@ -2111,7 +2111,7 @@
         <v>135694241</v>
       </c>
       <c r="B16" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>135695820</v>
       </c>
       <c r="B84" t="n">
-        <v>99198</v>
+        <v>99199</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>135693099</v>
       </c>
       <c r="B100" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>135693143</v>
       </c>
       <c r="B101" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>135693261</v>
       </c>
       <c r="B102" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>135693320</v>
       </c>
       <c r="B103" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>135693361</v>
       </c>
       <c r="B104" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>135693409</v>
       </c>
       <c r="B105" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>135693449</v>
       </c>
       <c r="B106" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>135694006</v>
       </c>
       <c r="B107" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>135694368</v>
       </c>
       <c r="B108" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>135695337</v>
       </c>
       <c r="B109" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>135695467</v>
       </c>
       <c r="B110" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>135695589</v>
       </c>
       <c r="B111" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>135695640</v>
       </c>
       <c r="B112" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>135695650</v>
       </c>
       <c r="B113" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>135695661</v>
       </c>
       <c r="B114" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>135695778</v>
       </c>
       <c r="B115" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>135695863</v>
       </c>
       <c r="B116" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>135695888</v>
       </c>
       <c r="B117" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>135695827</v>
       </c>
       <c r="B118" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 28376-2026 artfynd.xlsx
+++ b/artfynd/A 28376-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135693259</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135693412</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135693522</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135693681</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135693950</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135693987</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135694070</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135694346</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135694505</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135694965</v>
       </c>
       <c r="B11" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135695151</v>
       </c>
       <c r="B12" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135695441</v>
       </c>
       <c r="B13" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135693971</v>
       </c>
       <c r="B15" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135694241</v>
       </c>
       <c r="B16" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>135693150</v>
       </c>
       <c r="B40" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>135693173</v>
       </c>
       <c r="B41" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>135693178</v>
       </c>
       <c r="B42" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>135693517</v>
       </c>
       <c r="B43" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>135693630</v>
       </c>
       <c r="B44" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>135693671</v>
       </c>
       <c r="B45" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>135693676</v>
       </c>
       <c r="B46" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>135694781</v>
       </c>
       <c r="B47" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>135695032</v>
       </c>
       <c r="B48" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135695091</v>
       </c>
       <c r="B49" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>135695305</v>
       </c>
       <c r="B50" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>135695360</v>
       </c>
       <c r="B51" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>135695385</v>
       </c>
       <c r="B52" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>135695569</v>
       </c>
       <c r="B53" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>135695602</v>
       </c>
       <c r="B54" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>135695710</v>
       </c>
       <c r="B55" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>135695786</v>
       </c>
       <c r="B56" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>135695844</v>
       </c>
       <c r="B57" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>135694109</v>
       </c>
       <c r="B59" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>135693769</v>
       </c>
       <c r="B61" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>135695207</v>
       </c>
       <c r="B62" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>135695447</v>
       </c>
       <c r="B63" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>135693600</v>
       </c>
       <c r="B64" t="n">
-        <v>79530</v>
+        <v>79531</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>135694482</v>
       </c>
       <c r="B65" t="n">
-        <v>79530</v>
+        <v>79531</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>135694128</v>
       </c>
       <c r="B66" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>135694698</v>
       </c>
       <c r="B67" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>135695115</v>
       </c>
       <c r="B68" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>135695211</v>
       </c>
       <c r="B70" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>135694103</v>
       </c>
       <c r="B72" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>135694882</v>
       </c>
       <c r="B73" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>135695039</v>
       </c>
       <c r="B74" t="n">
-        <v>57631</v>
+        <v>57632</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>135694812</v>
       </c>
       <c r="B75" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>135695614</v>
       </c>
       <c r="B77" t="n">
-        <v>58417</v>
+        <v>58418</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>135693380</v>
       </c>
       <c r="B80" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>135695688</v>
       </c>
       <c r="B81" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>135695820</v>
       </c>
       <c r="B84" t="n">
-        <v>99199</v>
+        <v>99200</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>135693099</v>
       </c>
       <c r="B100" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>135693143</v>
       </c>
       <c r="B101" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>135693261</v>
       </c>
       <c r="B102" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>135693320</v>
       </c>
       <c r="B103" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>135693361</v>
       </c>
       <c r="B104" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>135693409</v>
       </c>
       <c r="B105" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>135693449</v>
       </c>
       <c r="B106" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>135694006</v>
       </c>
       <c r="B107" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>135694368</v>
       </c>
       <c r="B108" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>135695337</v>
       </c>
       <c r="B109" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>135695467</v>
       </c>
       <c r="B110" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>135695589</v>
       </c>
       <c r="B111" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>135695640</v>
       </c>
       <c r="B112" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>135695650</v>
       </c>
       <c r="B113" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>135695661</v>
       </c>
       <c r="B114" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>135695778</v>
       </c>
       <c r="B115" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>135695863</v>
       </c>
       <c r="B116" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>135695888</v>
       </c>
       <c r="B117" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>135695827</v>
       </c>
       <c r="B118" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>135693489</v>
       </c>
       <c r="B120" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>135693779</v>
       </c>
       <c r="B121" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>135695241</v>
       </c>
       <c r="B122" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>135695458</v>
       </c>
       <c r="B123" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>135695697</v>
       </c>
       <c r="B124" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>135694935</v>
       </c>
       <c r="B125" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>135695349</v>
       </c>
       <c r="B126" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 28376-2026 artfynd.xlsx
+++ b/artfynd/A 28376-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135693259</v>
       </c>
       <c r="B2" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135693412</v>
       </c>
       <c r="B3" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135693522</v>
       </c>
       <c r="B4" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135693681</v>
       </c>
       <c r="B5" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135693950</v>
       </c>
       <c r="B6" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135693987</v>
       </c>
       <c r="B7" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135694070</v>
       </c>
       <c r="B8" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135694346</v>
       </c>
       <c r="B9" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135694505</v>
       </c>
       <c r="B10" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135694965</v>
       </c>
       <c r="B11" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135695151</v>
       </c>
       <c r="B12" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135695441</v>
       </c>
       <c r="B13" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135693971</v>
       </c>
       <c r="B15" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135694241</v>
       </c>
       <c r="B16" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>135693150</v>
       </c>
       <c r="B40" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>135693173</v>
       </c>
       <c r="B41" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>135693178</v>
       </c>
       <c r="B42" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>135693517</v>
       </c>
       <c r="B43" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>135693630</v>
       </c>
       <c r="B44" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>135693671</v>
       </c>
       <c r="B45" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>135693676</v>
       </c>
       <c r="B46" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>135694781</v>
       </c>
       <c r="B47" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>135695032</v>
       </c>
       <c r="B48" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135695091</v>
       </c>
       <c r="B49" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>135695305</v>
       </c>
       <c r="B50" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>135695360</v>
       </c>
       <c r="B51" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>135695385</v>
       </c>
       <c r="B52" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>135695569</v>
       </c>
       <c r="B53" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>135695602</v>
       </c>
       <c r="B54" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>135695710</v>
       </c>
       <c r="B55" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>135695786</v>
       </c>
       <c r="B56" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>135695844</v>
       </c>
       <c r="B57" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>135694109</v>
       </c>
       <c r="B59" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>135693769</v>
       </c>
       <c r="B61" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>135695207</v>
       </c>
       <c r="B62" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>135695447</v>
       </c>
       <c r="B63" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>135693600</v>
       </c>
       <c r="B64" t="n">
-        <v>79531</v>
+        <v>79535</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>135694482</v>
       </c>
       <c r="B65" t="n">
-        <v>79531</v>
+        <v>79535</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>135694128</v>
       </c>
       <c r="B66" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>135694698</v>
       </c>
       <c r="B67" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>135695115</v>
       </c>
       <c r="B68" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>135695211</v>
       </c>
       <c r="B70" t="n">
-        <v>80564</v>
+        <v>80568</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>135694103</v>
       </c>
       <c r="B72" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>135694882</v>
       </c>
       <c r="B73" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>135695039</v>
       </c>
       <c r="B74" t="n">
-        <v>57632</v>
+        <v>57636</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>135694812</v>
       </c>
       <c r="B75" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>135695614</v>
       </c>
       <c r="B77" t="n">
-        <v>58418</v>
+        <v>58422</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>135693380</v>
       </c>
       <c r="B80" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>135695688</v>
       </c>
       <c r="B81" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>135695820</v>
       </c>
       <c r="B84" t="n">
-        <v>99200</v>
+        <v>99206</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>135693099</v>
       </c>
       <c r="B100" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>135693143</v>
       </c>
       <c r="B101" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>135693261</v>
       </c>
       <c r="B102" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>135693320</v>
       </c>
       <c r="B103" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>135693361</v>
       </c>
       <c r="B104" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>135693409</v>
       </c>
       <c r="B105" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>135693449</v>
       </c>
       <c r="B106" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>135694006</v>
       </c>
       <c r="B107" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>135694368</v>
       </c>
       <c r="B108" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>135695337</v>
       </c>
       <c r="B109" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>135695467</v>
       </c>
       <c r="B110" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>135695589</v>
       </c>
       <c r="B111" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>135695640</v>
       </c>
       <c r="B112" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>135695650</v>
       </c>
       <c r="B113" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>135695661</v>
       </c>
       <c r="B114" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>135695778</v>
       </c>
       <c r="B115" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>135695863</v>
       </c>
       <c r="B116" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>135695888</v>
       </c>
       <c r="B117" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>135695827</v>
       </c>
       <c r="B118" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>135693489</v>
       </c>
       <c r="B120" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>135693779</v>
       </c>
       <c r="B121" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>135695241</v>
       </c>
       <c r="B122" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>135695458</v>
       </c>
       <c r="B123" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>135695697</v>
       </c>
       <c r="B124" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>135694935</v>
       </c>
       <c r="B125" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>135695349</v>
       </c>
       <c r="B126" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 28376-2026 artfynd.xlsx
+++ b/artfynd/A 28376-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135693259</v>
       </c>
       <c r="B2" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135693412</v>
       </c>
       <c r="B3" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135693522</v>
       </c>
       <c r="B4" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135693681</v>
       </c>
       <c r="B5" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135693950</v>
       </c>
       <c r="B6" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135693987</v>
       </c>
       <c r="B7" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135694070</v>
       </c>
       <c r="B8" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135694346</v>
       </c>
       <c r="B9" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135694505</v>
       </c>
       <c r="B10" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135694965</v>
       </c>
       <c r="B11" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135695151</v>
       </c>
       <c r="B12" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135695441</v>
       </c>
       <c r="B13" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135693971</v>
       </c>
       <c r="B15" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135694241</v>
       </c>
       <c r="B16" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>135693150</v>
       </c>
       <c r="B40" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>135693173</v>
       </c>
       <c r="B41" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>135693178</v>
       </c>
       <c r="B42" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>135693517</v>
       </c>
       <c r="B43" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>135693630</v>
       </c>
       <c r="B44" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>135693671</v>
       </c>
       <c r="B45" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>135693676</v>
       </c>
       <c r="B46" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>135694781</v>
       </c>
       <c r="B47" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>135695032</v>
       </c>
       <c r="B48" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135695091</v>
       </c>
       <c r="B49" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>135695305</v>
       </c>
       <c r="B50" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>135695360</v>
       </c>
       <c r="B51" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>135695385</v>
       </c>
       <c r="B52" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>135695569</v>
       </c>
       <c r="B53" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>135695602</v>
       </c>
       <c r="B54" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>135695710</v>
       </c>
       <c r="B55" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>135695786</v>
       </c>
       <c r="B56" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>135695844</v>
       </c>
       <c r="B57" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>135694109</v>
       </c>
       <c r="B59" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>135693769</v>
       </c>
       <c r="B61" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>135695207</v>
       </c>
       <c r="B62" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>135695447</v>
       </c>
       <c r="B63" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>135693600</v>
       </c>
       <c r="B64" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>135694482</v>
       </c>
       <c r="B65" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>135694128</v>
       </c>
       <c r="B66" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>135694698</v>
       </c>
       <c r="B67" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>135695115</v>
       </c>
       <c r="B68" t="n">
-        <v>80458</v>
+        <v>80459</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>135695211</v>
       </c>
       <c r="B70" t="n">
-        <v>80568</v>
+        <v>80569</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>135694103</v>
       </c>
       <c r="B72" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>135694882</v>
       </c>
       <c r="B73" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>135695039</v>
       </c>
       <c r="B74" t="n">
-        <v>57636</v>
+        <v>57637</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>135694812</v>
       </c>
       <c r="B75" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>135695614</v>
       </c>
       <c r="B77" t="n">
-        <v>58422</v>
+        <v>58423</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>135693380</v>
       </c>
       <c r="B80" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>135695688</v>
       </c>
       <c r="B81" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>135695820</v>
       </c>
       <c r="B84" t="n">
-        <v>99206</v>
+        <v>99207</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>135693099</v>
       </c>
       <c r="B100" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>135693143</v>
       </c>
       <c r="B101" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>135693261</v>
       </c>
       <c r="B102" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>135693320</v>
       </c>
       <c r="B103" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>135693361</v>
       </c>
       <c r="B104" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>135693409</v>
       </c>
       <c r="B105" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>135693449</v>
       </c>
       <c r="B106" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>135694006</v>
       </c>
       <c r="B107" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>135694368</v>
       </c>
       <c r="B108" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>135695337</v>
       </c>
       <c r="B109" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>135695467</v>
       </c>
       <c r="B110" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>135695589</v>
       </c>
       <c r="B111" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>135695640</v>
       </c>
       <c r="B112" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>135695650</v>
       </c>
       <c r="B113" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>135695661</v>
       </c>
       <c r="B114" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>135695778</v>
       </c>
       <c r="B115" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>135695863</v>
       </c>
       <c r="B116" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>135695888</v>
       </c>
       <c r="B117" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>135695827</v>
       </c>
       <c r="B118" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>135693489</v>
       </c>
       <c r="B120" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>135693779</v>
       </c>
       <c r="B121" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>135695241</v>
       </c>
       <c r="B122" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>135695458</v>
       </c>
       <c r="B123" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>135695697</v>
       </c>
       <c r="B124" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>135694935</v>
       </c>
       <c r="B125" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>135695349</v>
       </c>
       <c r="B126" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
